--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\下载\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BAC2BD-2A00-458E-97E0-6BBCC108FB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9211A61-7948-45A0-9F9A-DE7834E7C91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="案件列表" sheetId="1" r:id="rId1"/>
@@ -61,18 +61,6 @@
     <t>介入阶段</t>
   </si>
   <si>
-    <t>原告/申请人</t>
-  </si>
-  <si>
-    <t>上诉人或第三人信息补充</t>
-  </si>
-  <si>
-    <t>补上诉人或补告信息补充</t>
-  </si>
-  <si>
-    <t>被告</t>
-  </si>
-  <si>
     <t>代理权限</t>
   </si>
   <si>
@@ -168,6 +156,22 @@
   </si>
   <si>
     <t>YYYY-MM-DD格式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>原告/申请人/侦察机关/检察院</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上诉人或第三人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被上诉人</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被告(人)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -175,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -195,6 +199,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,9 +228,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -598,124 +612,124 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Y2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,45 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9211A61-7948-45A0-9F9A-DE7834E7C91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFC03D3-AFDA-4350-807A-FAAB60D82481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="案件列表" sheetId="1" r:id="rId1"/>
+    <sheet name="业务列表" sheetId="1" r:id="rId1"/>
+    <sheet name="当事人列表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
-  <si>
-    <t>案件号</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
   <si>
     <t>委托日期</t>
   </si>
   <si>
-    <t>委托人</t>
-  </si>
-  <si>
-    <t>委托人身份证号/单位税号</t>
-  </si>
-  <si>
-    <t>委托人电话</t>
-  </si>
-  <si>
-    <t>案件类别</t>
-  </si>
-  <si>
     <t>案件来源</t>
   </si>
   <si>
@@ -94,9 +80,6 @@
     <t>执行助理律师</t>
   </si>
   <si>
-    <t>案件审核状态</t>
-  </si>
-  <si>
     <t>是否重大</t>
   </si>
   <si>
@@ -112,18 +95,12 @@
     <t>是否保全</t>
   </si>
   <si>
-    <t>是否删除</t>
-  </si>
-  <si>
     <t>保全开始日</t>
   </si>
   <si>
     <t>保全终止日</t>
   </si>
   <si>
-    <t>案号</t>
-  </si>
-  <si>
     <t>结案状态</t>
   </si>
   <si>
@@ -151,28 +128,218 @@
     <t>执行到期日</t>
   </si>
   <si>
+    <t>支行名称</t>
+  </si>
+  <si>
+    <t>抵/质押物信息</t>
+  </si>
+  <si>
+    <t>抵押物位置</t>
+  </si>
+  <si>
+    <t>客户经理</t>
+  </si>
+  <si>
+    <t>贷款类型</t>
+  </si>
+  <si>
+    <t>贷款账号</t>
+  </si>
+  <si>
+    <t>贷款本金</t>
+  </si>
+  <si>
+    <t>诉讼标的金额(含利息)</t>
+  </si>
+  <si>
+    <t>信用卡违约金</t>
+  </si>
+  <si>
+    <t>借款日</t>
+  </si>
+  <si>
+    <t>到期日</t>
+  </si>
+  <si>
+    <t>诉讼时效</t>
+  </si>
+  <si>
+    <t>收案日期</t>
+  </si>
+  <si>
+    <t>取材料人</t>
+  </si>
+  <si>
+    <t>诉前催收情况</t>
+  </si>
+  <si>
+    <t>盖章日</t>
+  </si>
+  <si>
+    <t>材料提交法院日</t>
+  </si>
+  <si>
+    <t>承办法官</t>
+  </si>
+  <si>
+    <t>裁判时间</t>
+  </si>
+  <si>
+    <t>裁判方式</t>
+  </si>
+  <si>
+    <t>裁判摘要</t>
+  </si>
+  <si>
+    <t>支持律师费金额</t>
+  </si>
+  <si>
+    <t>被告支付律师费金额</t>
+  </si>
+  <si>
+    <t>是否还清</t>
+  </si>
+  <si>
+    <t>是否有二审/再审</t>
+  </si>
+  <si>
+    <t>执行案号</t>
+  </si>
+  <si>
+    <t>执行立案时间</t>
+  </si>
+  <si>
+    <t>执行法官</t>
+  </si>
+  <si>
+    <t>借款人工作单位</t>
+  </si>
+  <si>
+    <t>是否为恢复执行</t>
+  </si>
+  <si>
+    <t>收取执行材料时间</t>
+  </si>
+  <si>
+    <t>执行材料提交法院时间</t>
+  </si>
+  <si>
+    <t>执行本金金额</t>
+  </si>
+  <si>
+    <t>执行律师费金额</t>
+  </si>
+  <si>
+    <t>财产调查情况</t>
+  </si>
+  <si>
+    <t>网络查控财产情况</t>
+  </si>
+  <si>
+    <t>承办人执行方案</t>
+  </si>
+  <si>
+    <t>法院执行措施</t>
+  </si>
+  <si>
+    <t>查封冻结时间</t>
+  </si>
+  <si>
+    <t>拍卖程序</t>
+  </si>
+  <si>
+    <t>拍卖变卖成交价</t>
+  </si>
+  <si>
+    <t>执行和解内容</t>
+  </si>
+  <si>
+    <t>终本时间</t>
+  </si>
+  <si>
+    <t>终本原因</t>
+  </si>
+  <si>
+    <t>终结执行时间</t>
+  </si>
+  <si>
+    <t>恢复执行时间</t>
+  </si>
+  <si>
+    <t>还清时间</t>
+  </si>
+  <si>
+    <t>执行回款总金额</t>
+  </si>
+  <si>
+    <t>执行回款来源</t>
+  </si>
+  <si>
+    <t>调解案件履行跟踪情况</t>
+  </si>
+  <si>
+    <t>当事人类型</t>
+  </si>
+  <si>
+    <t>姓名/名称</t>
+  </si>
+  <si>
+    <t>联系电话</t>
+  </si>
+  <si>
+    <t>身份证号/统一社会信用代码</t>
+  </si>
+  <si>
+    <t>联系地址</t>
+  </si>
+  <si>
+    <t>法定代表人</t>
+  </si>
+  <si>
+    <t>被告</t>
+  </si>
+  <si>
+    <t>李四</t>
+  </si>
+  <si>
     <t>必填</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>YYYY-MM-DD格式</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>原告/申请人/侦察机关/检察院</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>上诉人或第三人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>被上诉人</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>被告(人)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(示例) 湘生律(2025)银行案件第1号(必填)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025/2/22(必填)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行案件(必填)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>某某银行</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>委托人(必填)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>湘生律(2025)银行案件第1号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务类别</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>关联业务号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -191,6 +358,15 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -200,20 +376,19 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3D3D3"/>
+        <bgColor rgb="FFD3D3D3"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -228,14 +403,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -538,202 +712,437 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CI2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5546875" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="6" max="9" width="7.21875" customWidth="1"/>
-    <col min="10" max="10" width="10.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" customWidth="1"/>
-    <col min="15" max="16" width="15.5546875" customWidth="1"/>
-    <col min="17" max="17" width="27.5546875" customWidth="1"/>
-    <col min="18" max="18" width="7.21875" customWidth="1"/>
-    <col min="19" max="19" width="10.77734375" customWidth="1"/>
-    <col min="20" max="20" width="7.21875" customWidth="1"/>
-    <col min="21" max="21" width="6" customWidth="1"/>
-    <col min="22" max="23" width="7.21875" customWidth="1"/>
-    <col min="24" max="24" width="88.77734375" customWidth="1"/>
-    <col min="25" max="26" width="7.21875" customWidth="1"/>
-    <col min="27" max="29" width="9.5546875" customWidth="1"/>
-    <col min="30" max="30" width="7.21875" customWidth="1"/>
-    <col min="31" max="31" width="9.5546875" customWidth="1"/>
-    <col min="32" max="35" width="7.21875" customWidth="1"/>
-    <col min="36" max="37" width="8.44140625" customWidth="1"/>
-    <col min="38" max="38" width="4.77734375" customWidth="1"/>
-    <col min="39" max="40" width="7.21875" customWidth="1"/>
-    <col min="41" max="44" width="10.77734375" customWidth="1"/>
-    <col min="45" max="47" width="8.44140625" customWidth="1"/>
+    <col min="1" max="87" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AV1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="AW1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="AX1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="AY1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>42</v>
+      <c r="AZ1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>43</v>
-      </c>
+    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="2"/>
+      <c r="AV2" s="2"/>
+      <c r="AW2" s="2"/>
+      <c r="AX2" s="2"/>
+      <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
+      <c r="BB2" s="2"/>
+      <c r="BC2" s="2"/>
+      <c r="BD2" s="2"/>
+      <c r="BE2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BG2" s="2"/>
+      <c r="BH2" s="2"/>
+      <c r="BI2" s="2"/>
+      <c r="BJ2" s="2"/>
+      <c r="BK2" s="2"/>
+      <c r="BL2" s="2"/>
+      <c r="BM2" s="2"/>
+      <c r="BN2" s="2"/>
+      <c r="BO2" s="2"/>
+      <c r="BP2" s="2"/>
+      <c r="BQ2" s="2"/>
+      <c r="BR2" s="2"/>
+      <c r="BS2" s="2"/>
+      <c r="BT2" s="2"/>
+      <c r="BU2" s="2"/>
+      <c r="BV2" s="2"/>
+      <c r="BW2" s="2"/>
+      <c r="BX2" s="2"/>
+      <c r="BY2" s="2"/>
+      <c r="BZ2" s="2"/>
+      <c r="CA2" s="2"/>
+      <c r="CB2" s="2"/>
+      <c r="CC2" s="2"/>
+      <c r="CD2" s="2"/>
+      <c r="CE2" s="2"/>
+      <c r="CF2" s="2"/>
+      <c r="CG2" s="2"/>
+      <c r="CH2" s="2"/>
+      <c r="CI2" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFC03D3-AFDA-4350-807A-FAAB60D82481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5302F-4DA3-4946-863F-19B7A4EF903D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>委托日期</t>
   </si>
@@ -339,6 +339,10 @@
   </si>
   <si>
     <t>关联业务号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>案号</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -712,13 +716,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CI2"/>
+  <dimension ref="A1:CJ2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="87" width="18" customWidth="1"/>
+    <col min="1" max="88" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
@@ -804,184 +808,187 @@
         <v>25</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:87" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>94</v>
       </c>
@@ -1077,6 +1084,7 @@
       <c r="CG2" s="2"/>
       <c r="CH2" s="2"/>
       <c r="CI2" s="2"/>
+      <c r="CJ2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA5302F-4DA3-4946-863F-19B7A4EF903D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71229476-A795-4904-9BA9-6C32D9DFB437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="23040" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
   <si>
     <t>委托日期</t>
   </si>
@@ -302,18 +302,10 @@
     <t>李四</t>
   </si>
   <si>
-    <t>必填</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>(示例) 湘生律(2025)银行案件第1号(必填)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>2025/2/22(必填)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>银行案件(必填)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -322,10 +314,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>委托人(必填)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>湘生律(2025)银行案件第1号</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -343,6 +331,30 @@
   </si>
   <si>
     <t>案号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>侦查机关</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>检察院</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>二审检察机关</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>顾问到期日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意：以下为银行专属字段</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>委托人(必填，银行案件的委托银行也填作委托人)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -350,7 +362,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,6 +392,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="楷体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -407,13 +427,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -716,21 +739,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CJ2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CO2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="88" width="18" customWidth="1"/>
+    <col min="1" max="42" width="18" customWidth="1"/>
+    <col min="43" max="43" width="26.77734375" customWidth="1"/>
+    <col min="44" max="92" width="18" customWidth="1"/>
+    <col min="93" max="93" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:93" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -760,243 +786,258 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AQ1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:93" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="3">
+        <v>45710</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1012,9 +1053,7 @@
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="2" t="s">
-        <v>93</v>
-      </c>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1085,6 +1124,11 @@
       <c r="CH2" s="2"/>
       <c r="CI2" s="2"/>
       <c r="CJ2" s="2"/>
+      <c r="CK2" s="2"/>
+      <c r="CL2" s="2"/>
+      <c r="CM2" s="2"/>
+      <c r="CN2" s="2"/>
+      <c r="CO2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1095,14 +1139,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>85</v>
@@ -1125,13 +1169,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1140,7 +1184,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>91</v>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71229476-A795-4904-9BA9-6C32D9DFB437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9070804C-AA8C-4F80-8965-2070372E3E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="23040" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
   <si>
     <t>委托日期</t>
   </si>
@@ -355,6 +355,10 @@
   </si>
   <si>
     <t>委托人(必填，银行案件的委托银行也填作委托人)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>案件状态</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -739,16 +743,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CO2"/>
+  <dimension ref="A1:CP2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="42" width="18" customWidth="1"/>
     <col min="43" max="43" width="26.77734375" customWidth="1"/>
-    <col min="44" max="92" width="18" customWidth="1"/>
-    <col min="93" max="93" width="23" customWidth="1"/>
+    <col min="44" max="93" width="18" customWidth="1"/>
+    <col min="94" max="94" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -882,154 +886,157 @@
         <v>35</v>
       </c>
       <c r="AS1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:93" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1129,6 +1136,7 @@
       <c r="CM2" s="2"/>
       <c r="CN2" s="2"/>
       <c r="CO2" s="2"/>
+      <c r="CP2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9070804C-AA8C-4F80-8965-2070372E3E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAE8E03-3729-46CB-865E-20B707EE6B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
   <si>
     <t>委托日期</t>
   </si>
@@ -359,6 +359,22 @@
   </si>
   <si>
     <t>案件状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷委托人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷原告</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷被告</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>以下为快捷当事人导入，如有其他类型或详细信息请于当事人列表登记</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -366,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,6 +420,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="楷体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -431,7 +454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -439,6 +462,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -743,16 +769,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CP2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CT2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="42" width="18" customWidth="1"/>
-    <col min="43" max="43" width="26.77734375" customWidth="1"/>
-    <col min="44" max="93" width="18" customWidth="1"/>
-    <col min="94" max="94" width="23" customWidth="1"/>
+    <col min="1" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="61.08984375" customWidth="1"/>
+    <col min="5" max="46" width="18" customWidth="1"/>
+    <col min="47" max="47" width="26.81640625" customWidth="1"/>
+    <col min="48" max="97" width="18" customWidth="1"/>
+    <col min="98" max="98" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -762,281 +790,293 @@
       <c r="C1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AU1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:94" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:98" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1137,6 +1177,10 @@
       <c r="CN2" s="2"/>
       <c r="CO2" s="2"/>
       <c r="CP2" s="2"/>
+      <c r="CQ2" s="2"/>
+      <c r="CR2" s="2"/>
+      <c r="CS2" s="2"/>
+      <c r="CT2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1147,7 +1191,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
   </cols>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAE8E03-3729-46CB-865E-20B707EE6B21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34768391-2CBE-497F-866C-6659F3BF8E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
   <si>
     <t>委托日期</t>
   </si>
@@ -375,6 +375,14 @@
   </si>
   <si>
     <t>以下为快捷当事人导入，如有其他类型或详细信息请于当事人列表登记</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行要求案件状态</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>缺少具体材料</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -769,18 +777,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CT2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" customWidth="1"/>
+    <col min="4" max="4" width="61.109375" customWidth="1"/>
     <col min="5" max="46" width="18" customWidth="1"/>
-    <col min="47" max="47" width="26.81640625" customWidth="1"/>
-    <col min="48" max="97" width="18" customWidth="1"/>
-    <col min="98" max="98" width="23" customWidth="1"/>
+    <col min="47" max="47" width="26.77734375" customWidth="1"/>
+    <col min="48" max="49" width="18" customWidth="1"/>
+    <col min="50" max="50" width="21.21875" customWidth="1"/>
+    <col min="51" max="99" width="18" customWidth="1"/>
+    <col min="100" max="100" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -929,154 +939,160 @@
         <v>107</v>
       </c>
       <c r="AX1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AY1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="BM1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:98" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:100" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1181,6 +1197,8 @@
       <c r="CR2" s="2"/>
       <c r="CS2" s="2"/>
       <c r="CT2" s="2"/>
+      <c r="CU2" s="2"/>
+      <c r="CV2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1191,7 +1209,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
   </cols>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34768391-2CBE-497F-866C-6659F3BF8E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24FA89C-22F2-4DA1-9C26-B1F663CCF71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-132" yWindow="-132" windowWidth="30984" windowHeight="16824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
   <si>
     <t>委托日期</t>
   </si>
@@ -383,6 +383,18 @@
   </si>
   <si>
     <t>缺少具体材料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷第三人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷担保人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式为 姓名1-身份证号1，姓名2-身份证号2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -390,7 +402,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,6 +447,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="楷体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -462,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -475,6 +495,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -777,20 +798,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CV2"/>
+  <dimension ref="A1:CX2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="61.109375" customWidth="1"/>
-    <col min="5" max="46" width="18" customWidth="1"/>
-    <col min="47" max="47" width="26.77734375" customWidth="1"/>
-    <col min="48" max="49" width="18" customWidth="1"/>
-    <col min="50" max="50" width="21.21875" customWidth="1"/>
-    <col min="51" max="99" width="18" customWidth="1"/>
-    <col min="100" max="100" width="23" customWidth="1"/>
+    <col min="5" max="48" width="18" customWidth="1"/>
+    <col min="49" max="49" width="26.77734375" customWidth="1"/>
+    <col min="50" max="51" width="18" customWidth="1"/>
+    <col min="52" max="52" width="21.21875" customWidth="1"/>
+    <col min="53" max="101" width="18" customWidth="1"/>
+    <col min="102" max="102" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -813,286 +834,292 @@
         <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AU1" s="4" t="s">
+      <c r="AW1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:102" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1102,7 +1129,9 @@
       <c r="C2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1199,6 +1228,8 @@
       <c r="CT2" s="2"/>
       <c r="CU2" s="2"/>
       <c r="CV2" s="2"/>
+      <c r="CW2" s="2"/>
+      <c r="CX2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24FA89C-22F2-4DA1-9C26-B1F663CCF71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937EC2A6-8354-451C-A9F2-64CE1B5444C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-132" yWindow="-132" windowWidth="30984" windowHeight="16824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
   <si>
     <t>委托日期</t>
   </si>
@@ -394,7 +394,59 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>格式为 姓名1-身份证号1，姓名2-身份证号2</t>
+    <t>如有多个当事人，格式为 姓名1-身份证号1，姓名2-身份证号2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷委托人身份证号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷委托人电话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷原告身份证号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷原告电话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷被告身份证号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷被告电话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷第三人身份证号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷第三人电话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷借款人</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷借款人身份证号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷借款人电话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷担保人身份证号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>快捷担保人电话</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -798,20 +850,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CX2"/>
+  <dimension ref="A1:DL2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="61.109375" customWidth="1"/>
-    <col min="5" max="48" width="18" customWidth="1"/>
-    <col min="49" max="49" width="26.77734375" customWidth="1"/>
-    <col min="50" max="51" width="18" customWidth="1"/>
-    <col min="52" max="52" width="21.21875" customWidth="1"/>
-    <col min="53" max="101" width="18" customWidth="1"/>
-    <col min="102" max="102" width="23" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="22.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" customWidth="1"/>
+    <col min="16" max="16" width="19.77734375" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="22.109375" customWidth="1"/>
+    <col min="19" max="19" width="19.77734375" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" customWidth="1"/>
+    <col min="22" max="22" width="20.33203125" customWidth="1"/>
+    <col min="23" max="62" width="18" customWidth="1"/>
+    <col min="63" max="63" width="26.77734375" customWidth="1"/>
+    <col min="64" max="65" width="18" customWidth="1"/>
+    <col min="66" max="66" width="21.21875" customWidth="1"/>
+    <col min="67" max="115" width="18" customWidth="1"/>
+    <col min="116" max="116" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:116" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -828,298 +898,338 @@
         <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="U1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AW1" s="4" t="s">
+      <c r="BK1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:102" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:116" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1230,6 +1340,20 @@
       <c r="CV2" s="2"/>
       <c r="CW2" s="2"/>
       <c r="CX2" s="2"/>
+      <c r="CY2" s="2"/>
+      <c r="CZ2" s="2"/>
+      <c r="DA2" s="2"/>
+      <c r="DB2" s="2"/>
+      <c r="DC2" s="2"/>
+      <c r="DD2" s="2"/>
+      <c r="DE2" s="2"/>
+      <c r="DF2" s="2"/>
+      <c r="DG2" s="2"/>
+      <c r="DH2" s="2"/>
+      <c r="DI2" s="2"/>
+      <c r="DJ2" s="2"/>
+      <c r="DK2" s="2"/>
+      <c r="DL2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937EC2A6-8354-451C-A9F2-64CE1B5444C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66081D6A-37B2-429A-8FBF-76F8EF278740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-132" yWindow="-132" windowWidth="30984" windowHeight="16824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>委托日期</t>
   </si>
@@ -447,6 +447,10 @@
   </si>
   <si>
     <t>快捷担保人电话</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二助理律师</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -850,38 +854,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DL2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:DM2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="61.109375" customWidth="1"/>
+    <col min="4" max="4" width="61.08984375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="6" max="6" width="23.6328125" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="22.88671875" customWidth="1"/>
-    <col min="10" max="10" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="22.90625" customWidth="1"/>
+    <col min="10" max="10" width="19.6328125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
-    <col min="13" max="13" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="22.36328125" customWidth="1"/>
+    <col min="13" max="13" width="19.08984375" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="23.44140625" customWidth="1"/>
-    <col min="16" max="16" width="19.77734375" customWidth="1"/>
+    <col min="15" max="15" width="23.453125" customWidth="1"/>
+    <col min="16" max="16" width="19.81640625" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="22.109375" customWidth="1"/>
-    <col min="19" max="19" width="19.77734375" customWidth="1"/>
+    <col min="18" max="18" width="22.08984375" customWidth="1"/>
+    <col min="19" max="19" width="19.81640625" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" customWidth="1"/>
-    <col min="22" max="22" width="20.33203125" customWidth="1"/>
-    <col min="23" max="62" width="18" customWidth="1"/>
-    <col min="63" max="63" width="26.77734375" customWidth="1"/>
-    <col min="64" max="65" width="18" customWidth="1"/>
-    <col min="66" max="66" width="21.21875" customWidth="1"/>
-    <col min="67" max="115" width="18" customWidth="1"/>
-    <col min="116" max="116" width="23" customWidth="1"/>
+    <col min="21" max="21" width="22.6328125" customWidth="1"/>
+    <col min="22" max="22" width="20.36328125" customWidth="1"/>
+    <col min="23" max="63" width="18" customWidth="1"/>
+    <col min="64" max="64" width="26.81640625" customWidth="1"/>
+    <col min="65" max="66" width="18" customWidth="1"/>
+    <col min="67" max="67" width="21.1796875" customWidth="1"/>
+    <col min="68" max="116" width="18" customWidth="1"/>
+    <col min="117" max="117" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:117" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -1007,229 +1011,232 @@
         <v>16</v>
       </c>
       <c r="AQ1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="BK1" s="4" t="s">
+      <c r="BL1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:116" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:117" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1354,6 +1361,7 @@
       <c r="DJ2" s="2"/>
       <c r="DK2" s="2"/>
       <c r="DL2" s="2"/>
+      <c r="DM2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1364,7 +1372,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="18" customWidth="1"/>
   </cols>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66081D6A-37B2-429A-8FBF-76F8EF278740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5171F-DAB1-43C3-9958-FDF3E43F294B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="134">
   <si>
     <t>委托日期</t>
   </si>
@@ -451,6 +451,17 @@
   </si>
   <si>
     <t>第二助理律师</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>保证到期日</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行和解到期日</t>
+  </si>
+  <si>
+    <t>执行和解案件履行跟踪情况</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -854,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DM2"/>
+  <dimension ref="A1:DP2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -881,11 +892,13 @@
     <col min="64" max="64" width="26.81640625" customWidth="1"/>
     <col min="65" max="66" width="18" customWidth="1"/>
     <col min="67" max="67" width="21.1796875" customWidth="1"/>
-    <col min="68" max="116" width="18" customWidth="1"/>
-    <col min="117" max="117" width="23" customWidth="1"/>
+    <col min="68" max="111" width="18" customWidth="1"/>
+    <col min="112" max="112" width="25.08984375" customWidth="1"/>
+    <col min="113" max="119" width="18" customWidth="1"/>
+    <col min="120" max="120" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -1119,124 +1132,133 @@
         <v>46</v>
       </c>
       <c r="CA1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="CB1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="DI1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:117" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:120" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1362,6 +1384,9 @@
       <c r="DK2" s="2"/>
       <c r="DL2" s="2"/>
       <c r="DM2" s="2"/>
+      <c r="DN2" s="2"/>
+      <c r="DO2" s="2"/>
+      <c r="DP2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C5171F-DAB1-43C3-9958-FDF3E43F294B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5F0B3-814B-4B37-8591-AAD0843525D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
   <si>
     <t>委托日期</t>
   </si>
@@ -462,6 +462,22 @@
   </si>
   <si>
     <t>执行和解案件履行跟踪情况</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻结开始日期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冻结截止日期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>查封开始日期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>查封截止日期</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -865,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DP2"/>
+  <dimension ref="A1:DT2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -892,13 +908,13 @@
     <col min="64" max="64" width="26.81640625" customWidth="1"/>
     <col min="65" max="66" width="18" customWidth="1"/>
     <col min="67" max="67" width="21.1796875" customWidth="1"/>
-    <col min="68" max="111" width="18" customWidth="1"/>
-    <col min="112" max="112" width="25.08984375" customWidth="1"/>
-    <col min="113" max="119" width="18" customWidth="1"/>
-    <col min="120" max="120" width="23" customWidth="1"/>
+    <col min="68" max="115" width="18" customWidth="1"/>
+    <col min="116" max="116" width="25.08984375" customWidth="1"/>
+    <col min="117" max="123" width="18" customWidth="1"/>
+    <col min="124" max="124" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -1219,46 +1235,58 @@
         <v>73</v>
       </c>
       <c r="DD1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="DH1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1387,6 +1415,10 @@
       <c r="DN2" s="2"/>
       <c r="DO2" s="2"/>
       <c r="DP2" s="2"/>
+      <c r="DQ2" s="2"/>
+      <c r="DR2" s="2"/>
+      <c r="DS2" s="2"/>
+      <c r="DT2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B5F0B3-814B-4B37-8591-AAD0843525D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CA7552-4BC0-4583-88FB-340992D3A986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
   <si>
     <t>委托日期</t>
   </si>
@@ -478,6 +478,10 @@
   </si>
   <si>
     <t>查封截止日期</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>诉讼标的额</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -881,7 +885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DT2"/>
+  <dimension ref="A1:DU2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -904,17 +908,17 @@
     <col min="20" max="20" width="18" customWidth="1"/>
     <col min="21" max="21" width="22.6328125" customWidth="1"/>
     <col min="22" max="22" width="20.36328125" customWidth="1"/>
-    <col min="23" max="63" width="18" customWidth="1"/>
-    <col min="64" max="64" width="26.81640625" customWidth="1"/>
-    <col min="65" max="66" width="18" customWidth="1"/>
-    <col min="67" max="67" width="21.1796875" customWidth="1"/>
-    <col min="68" max="115" width="18" customWidth="1"/>
-    <col min="116" max="116" width="25.08984375" customWidth="1"/>
-    <col min="117" max="123" width="18" customWidth="1"/>
-    <col min="124" max="124" width="23" customWidth="1"/>
+    <col min="23" max="64" width="18" customWidth="1"/>
+    <col min="65" max="65" width="26.81640625" customWidth="1"/>
+    <col min="66" max="67" width="18" customWidth="1"/>
+    <col min="68" max="68" width="21.1796875" customWidth="1"/>
+    <col min="69" max="116" width="18" customWidth="1"/>
+    <col min="117" max="117" width="25.08984375" customWidth="1"/>
+    <col min="118" max="124" width="18" customWidth="1"/>
+    <col min="125" max="125" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -992,301 +996,304 @@
         <v>3</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="BL1" s="4" t="s">
+      <c r="BM1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:124" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:125" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1419,6 +1426,7 @@
       <c r="DR2" s="2"/>
       <c r="DS2" s="2"/>
       <c r="DT2" s="2"/>
+      <c r="DU2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CA7552-4BC0-4583-88FB-340992D3A986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5915C15F-19B0-4F32-B241-F2C08FB353E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
     <sheet name="当事人列表" sheetId="2" r:id="rId2"/>
+    <sheet name="下拉菜单" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="233">
   <si>
     <t>委托日期</t>
   </si>
@@ -483,13 +484,420 @@
   <si>
     <t>诉讼标的额</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>民事案件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行案件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刑事案件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>行政案件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>非诉业务</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行案件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劳动仲裁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>商事仲裁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>法律顾问业务</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法律援助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>民事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法律援助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刑事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法律援助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行政</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF6AAB73"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定收费</t>
+  </si>
+  <si>
+    <t>风险收费</t>
+  </si>
+  <si>
+    <t>免费（顾问单位）</t>
+  </si>
+  <si>
+    <t>免费（法律援助）</t>
+  </si>
+  <si>
+    <t>免费（亲戚）</t>
+  </si>
+  <si>
+    <t>免费（原阶段已包含）</t>
+  </si>
+  <si>
+    <t>建设银行</t>
+  </si>
+  <si>
+    <t>邮政银行</t>
+  </si>
+  <si>
+    <t>农村商业银行</t>
+  </si>
+  <si>
+    <t>工商银行</t>
+  </si>
+  <si>
+    <t>交通银行</t>
+  </si>
+  <si>
+    <t>住房公积金</t>
+  </si>
+  <si>
+    <t>长沙村镇银行</t>
+  </si>
+  <si>
+    <t>中国银行</t>
+  </si>
+  <si>
+    <t>保靖支行</t>
+  </si>
+  <si>
+    <t>凤凰支行</t>
+  </si>
+  <si>
+    <t>古丈支行</t>
+  </si>
+  <si>
+    <t>花垣支行</t>
+  </si>
+  <si>
+    <t>吉大支行</t>
+  </si>
+  <si>
+    <t>吉首支行</t>
+  </si>
+  <si>
+    <t>龙山支行</t>
+  </si>
+  <si>
+    <t>泸溪支行</t>
+  </si>
+  <si>
+    <t>文艺路支行</t>
+  </si>
+  <si>
+    <t>乾城支行</t>
+  </si>
+  <si>
+    <t>乾州支行</t>
+  </si>
+  <si>
+    <t>人民路支行</t>
+  </si>
+  <si>
+    <t>营业部</t>
+  </si>
+  <si>
+    <t>永顺支行</t>
+  </si>
+  <si>
+    <t>矮寨支行</t>
+  </si>
+  <si>
+    <t>城东支行</t>
+  </si>
+  <si>
+    <t>城南支行</t>
+  </si>
+  <si>
+    <t>丹青支行</t>
+  </si>
+  <si>
+    <t>河溪支行</t>
+  </si>
+  <si>
+    <t>马颈坳支行</t>
+  </si>
+  <si>
+    <t>排吼支行</t>
+  </si>
+  <si>
+    <t>社塘坡支行</t>
+  </si>
+  <si>
+    <t>太平支行</t>
+  </si>
+  <si>
+    <t>雅溪支行</t>
+  </si>
+  <si>
+    <t>寒阳支行</t>
+  </si>
+  <si>
+    <t>团结西路支行</t>
+  </si>
+  <si>
+    <t>湘西州分行</t>
+  </si>
+  <si>
+    <t>经开区支行</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>峒河支行</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>写诉讼状中</t>
+  </si>
+  <si>
+    <t>资料不足</t>
+  </si>
+  <si>
+    <t>移交法院排队立案</t>
+  </si>
+  <si>
+    <t>诉讼立案</t>
+  </si>
+  <si>
+    <t>已开庭</t>
+  </si>
+  <si>
+    <t>已裁判</t>
+  </si>
+  <si>
+    <t>债务履行完毕结案</t>
+  </si>
+  <si>
+    <t>银行要求撤诉</t>
+  </si>
+  <si>
+    <t>终结执行</t>
+  </si>
+  <si>
+    <t>跟进调解履行情况</t>
+  </si>
+  <si>
+    <t>写执行申请资料</t>
+  </si>
+  <si>
+    <t>移交法院执行手续</t>
+  </si>
+  <si>
+    <t>执行排队立案中</t>
+  </si>
+  <si>
+    <t>执行和解</t>
+  </si>
+  <si>
+    <t>网络查控资产情况</t>
+  </si>
+  <si>
+    <t>扣划工资工积金处置抵押物</t>
+  </si>
+  <si>
+    <t>询价查看不动产情况</t>
+  </si>
+  <si>
+    <t>拍卖抵押物</t>
+  </si>
+  <si>
+    <t>终本</t>
+  </si>
+  <si>
+    <t>恢复执行中</t>
+  </si>
+  <si>
+    <t>银行要求暂不起诉</t>
+  </si>
+  <si>
+    <t>银行未交诉讼费撤诉</t>
+  </si>
+  <si>
+    <t>被告已还清不起诉</t>
+  </si>
+  <si>
+    <t>被告已还清撤诉</t>
+  </si>
+  <si>
+    <t>执行盖章中</t>
+  </si>
+  <si>
+    <t>诉讼盖章中</t>
+  </si>
+  <si>
+    <t>资料未齐全</t>
+  </si>
+  <si>
+    <t>资料齐全律所正在准备诉状或正在盖章</t>
+  </si>
+  <si>
+    <t>资料齐全已移交法院排队</t>
+  </si>
+  <si>
+    <t>立案后调解</t>
+  </si>
+  <si>
+    <t>立案前调解</t>
+  </si>
+  <si>
+    <t>已立案我行申请撤诉</t>
+  </si>
+  <si>
+    <t>未立案我行申请不诉</t>
+  </si>
+  <si>
+    <t>已立案未判决</t>
+  </si>
+  <si>
+    <t>已立案判决未申请执行</t>
+  </si>
+  <si>
+    <t>已申请执行</t>
+  </si>
+  <si>
+    <t>执行中</t>
+  </si>
+  <si>
+    <t>终结本次执行</t>
+  </si>
+  <si>
+    <t>执行完毕</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,6 +950,45 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF6AAB73"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF606266"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF606266"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -569,7 +1016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -583,6 +1030,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -885,40 +1348,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DU2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:DU3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="61.08984375" customWidth="1"/>
+    <col min="4" max="4" width="61.109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="23.6328125" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="22.90625" customWidth="1"/>
-    <col min="10" max="10" width="19.6328125" customWidth="1"/>
+    <col min="9" max="9" width="22.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="22.36328125" customWidth="1"/>
-    <col min="13" max="13" width="19.08984375" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="23.453125" customWidth="1"/>
-    <col min="16" max="16" width="19.81640625" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" customWidth="1"/>
+    <col min="16" max="16" width="19.77734375" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="22.08984375" customWidth="1"/>
-    <col min="19" max="19" width="19.81640625" customWidth="1"/>
+    <col min="18" max="18" width="22.109375" customWidth="1"/>
+    <col min="19" max="19" width="19.77734375" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="22.6328125" customWidth="1"/>
-    <col min="22" max="22" width="20.36328125" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" customWidth="1"/>
+    <col min="22" max="22" width="20.33203125" customWidth="1"/>
     <col min="23" max="64" width="18" customWidth="1"/>
-    <col min="65" max="65" width="26.81640625" customWidth="1"/>
+    <col min="65" max="65" width="26.77734375" customWidth="1"/>
     <col min="66" max="67" width="18" customWidth="1"/>
-    <col min="68" max="68" width="21.1796875" customWidth="1"/>
+    <col min="68" max="68" width="21.21875" customWidth="1"/>
     <col min="69" max="116" width="18" customWidth="1"/>
-    <col min="117" max="117" width="25.08984375" customWidth="1"/>
+    <col min="117" max="117" width="25.109375" customWidth="1"/>
     <col min="118" max="124" width="18" customWidth="1"/>
     <col min="125" max="125" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:125" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:125">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -1293,7 +1756,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:125" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:125">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1428,71 +1891,507 @@
       <c r="DT2" s="2"/>
       <c r="DU2" s="2"/>
     </row>
+    <row r="3" spans="1:125">
+      <c r="B3" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AF1048576" xr:uid="{42D0D285-222E-4112-8984-9734F9F28D29}">
+      <formula1>"一般代理,特别代理"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="AU1:AY1048576 CO1:CO1048576 CP1:CP1048576 CU1:CU1048576" xr:uid="{4464FD37-F9F7-4812-BDD0-74E3B51C122E}">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="CK1:CK1048576" xr:uid="{DF26E270-6DC0-4AFD-AA4B-27A7D308895F}">
+      <formula1>"判决,裁定,调解"</formula1>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须使用-或/进行分隔" sqref="B1:B1048576" xr:uid="{76EC1C81-A985-4B80-8417-4F39E45BF715}">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须为-或/" sqref="AC1:AC1048576 AK1:AK1048576 AL1:AL1048576 AM1:AM1048576 AZ1:AZ1048576 BA1:BA1048576 BE1:BE1048576 BG1:BG1048576 BI1:BI1048576 BJ1:BJ1048576 BK1:BK1048576 BL1:BL1048576 BY1:BY1048576 BZ1:BZ1048576 CB1:CB1048576 CA1:CA1048576 CC1:CC1048576 CG1:CG1048576 CH1:CH1048576 CJ1:CJ1048576 CR1:CR1048576 CV1:CV1048576 CW1:CW1048576 DD1:DD1048576 DE1:DE1048576 DF1:DF1048576 DG1:DG1048576 DH1:DH1048576 DL1:DL1048576 DN1:DN1048576 DP1:DP1048576 DQ1:DQ1048576 DR1:DR1048576" xr:uid="{CA5C5D4D-7B3F-4AD6-8F9A-9FFBDB572669}">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="当前输入格式非纯数字格式" sqref="AB1:AB1048576 BF1:BF1048576 BH1:BH1048576 BV1:BV1048576 BW1:BW1048576 BX1:BX1048576 CM1:CM1048576 CN1:CN1048576 CX1:CX1048576 CY1:CY1048576 DJ1:DJ1048576 DS1:DS1048576" xr:uid="{2CD1D548-3868-45C8-A9C8-D03CD7D9AEAE}">
+      <formula1>-9999999999</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{FC007753-7F4D-4AE2-8418-3AD9DF4FEF31}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$A$1:$A$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{42F40340-F080-43EB-9AA5-0BBE54FBF44B}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$B$1:$B$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>Y1:Y1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" errorStyle="information" allowBlank="1" showInputMessage="1" promptTitle="提示" prompt="如为银行案件请点击单元格右侧下拉菜单选择对应银行" xr:uid="{D4A0A9C7-A2CD-4941-82DA-EF0FEB00F59C}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$C$1:$C$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{816B8064-D8D8-4C43-93EA-4CCED8835A53}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$D$1:$D$29</xm:f>
+          </x14:formula1>
+          <xm:sqref>BN1:BN1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{30DA0B9C-AA69-412C-966A-84DD4AAAAF56}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$E$1:$E$26</xm:f>
+          </x14:formula1>
+          <xm:sqref>BO1:BO1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{44A50DD6-510D-4E7B-A823-C35FED0FE2D4}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$F$1:$F$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>BP1:BP1048576</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="27.77734375" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068C94DB-3A5F-4F6E-BA5A-436C41DCF235}">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" customWidth="1"/>
+    <col min="6" max="6" width="33.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" t="s">
-        <v>92</v>
+    <row r="1" spans="1:6">
+      <c r="A1" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7"/>
+      <c r="D13" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="D14" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="D15" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="D16" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5">
+      <c r="D17" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="18" spans="4:5">
+      <c r="D18" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="4:5">
+      <c r="D19" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="4:5">
+      <c r="D20" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="4:5">
+      <c r="D21" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5">
+      <c r="D22" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5">
+      <c r="D23" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5">
+      <c r="D24" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5">
+      <c r="D25" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5">
+      <c r="D26" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="27" spans="4:5">
+      <c r="D27" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5">
+      <c r="D28" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5">
+      <c r="D29" s="10" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5915C15F-19B0-4F32-B241-F2C08FB353E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EC683F-0ED5-414A-B1E2-DA564BB3F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -1016,7 +1016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1046,6 +1046,11 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1354,22 +1359,22 @@
     <col min="1" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="61.109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="15" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="22.88671875" customWidth="1"/>
+    <col min="9" max="9" width="22.88671875" style="15" customWidth="1"/>
     <col min="10" max="10" width="19.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="22.33203125" customWidth="1"/>
+    <col min="12" max="12" width="22.33203125" style="15" customWidth="1"/>
     <col min="13" max="13" width="19.109375" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="23.44140625" customWidth="1"/>
+    <col min="15" max="15" width="23.44140625" style="15" customWidth="1"/>
     <col min="16" max="16" width="19.77734375" customWidth="1"/>
     <col min="17" max="17" width="18" customWidth="1"/>
-    <col min="18" max="18" width="22.109375" customWidth="1"/>
+    <col min="18" max="18" width="22.109375" style="15" customWidth="1"/>
     <col min="19" max="19" width="19.77734375" customWidth="1"/>
     <col min="20" max="20" width="18" customWidth="1"/>
-    <col min="21" max="21" width="22.6640625" customWidth="1"/>
+    <col min="21" max="21" width="22.6640625" style="15" customWidth="1"/>
     <col min="22" max="22" width="20.33203125" customWidth="1"/>
     <col min="23" max="64" width="18" customWidth="1"/>
     <col min="65" max="65" width="26.77734375" customWidth="1"/>
@@ -1397,7 +1402,7 @@
       <c r="E1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1406,7 +1411,7 @@
       <c r="H1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="13" t="s">
         <v>119</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1415,7 +1420,7 @@
       <c r="K1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="13" t="s">
         <v>121</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -1424,7 +1429,7 @@
       <c r="N1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="13" t="s">
         <v>123</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1433,7 +1438,7 @@
       <c r="Q1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="13" t="s">
         <v>126</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1442,7 +1447,7 @@
       <c r="T1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="13" t="s">
         <v>128</v>
       </c>
       <c r="V1" s="1" t="s">
@@ -1770,22 +1775,22 @@
         <v>116</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="14"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="I2" s="14"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="L2" s="14"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="O2" s="14"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="R2" s="14"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
+      <c r="U2" s="14"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
@@ -1967,15 +1972,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="27.77734375" customWidth="1"/>
+    <col min="5" max="5" width="27.77734375" style="15" customWidth="1"/>
     <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="9" max="9" width="41.77734375" customWidth="1"/>
+    <col min="10" max="10" width="46.109375" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
@@ -1988,7 +1996,7 @@
       <c r="D1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="13" t="s">
         <v>88</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1998,29 +2006,29 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>95</v>
-      </c>
+    <row r="2" spans="1:11">
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="I2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="I3" t="s">
         <v>96</v>
       </c>
-      <c r="B3" t="s">
+      <c r="J3" t="s">
         <v>91</v>
       </c>
-      <c r="C3" t="s">
+      <c r="K3" t="s">
         <v>92</v>
       </c>
     </row>

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79EC683F-0ED5-414A-B1E2-DA564BB3F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED45482-E67F-4396-9CDA-BBCE7D0FD948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="业务列表" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="235">
   <si>
     <t>委托日期</t>
   </si>
@@ -776,121 +776,133 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>诉讼立案</t>
+  </si>
+  <si>
+    <t>已开庭</t>
+  </si>
+  <si>
+    <t>已裁判</t>
+  </si>
+  <si>
+    <t>债务履行完毕结案</t>
+  </si>
+  <si>
+    <t>银行要求撤诉</t>
+  </si>
+  <si>
+    <t>终结执行</t>
+  </si>
+  <si>
+    <t>跟进调解履行情况</t>
+  </si>
+  <si>
+    <t>写执行申请资料</t>
+  </si>
+  <si>
+    <t>移交法院执行手续</t>
+  </si>
+  <si>
+    <t>执行排队立案中</t>
+  </si>
+  <si>
+    <t>执行和解</t>
+  </si>
+  <si>
+    <t>网络查控资产情况</t>
+  </si>
+  <si>
+    <t>扣划工资工积金处置抵押物</t>
+  </si>
+  <si>
+    <t>询价查看不动产情况</t>
+  </si>
+  <si>
+    <t>拍卖抵押物</t>
+  </si>
+  <si>
+    <t>终本</t>
+  </si>
+  <si>
+    <t>恢复执行中</t>
+  </si>
+  <si>
+    <t>银行未交诉讼费撤诉</t>
+  </si>
+  <si>
+    <t>被告已还清不起诉</t>
+  </si>
+  <si>
+    <t>被告已还清撤诉</t>
+  </si>
+  <si>
+    <t>执行盖章中</t>
+  </si>
+  <si>
+    <t>诉讼盖章中</t>
+  </si>
+  <si>
+    <t>资料未齐全</t>
+  </si>
+  <si>
+    <t>资料齐全律所正在准备诉状或正在盖章</t>
+  </si>
+  <si>
+    <t>资料齐全已移交法院排队</t>
+  </si>
+  <si>
+    <t>立案后调解</t>
+  </si>
+  <si>
+    <t>立案前调解</t>
+  </si>
+  <si>
+    <t>已立案我行申请撤诉</t>
+  </si>
+  <si>
+    <t>未立案我行申请不诉</t>
+  </si>
+  <si>
+    <t>已立案未判决</t>
+  </si>
+  <si>
+    <t>已立案判决未申请执行</t>
+  </si>
+  <si>
+    <t>已申请执行</t>
+  </si>
+  <si>
+    <t>执行中</t>
+  </si>
+  <si>
+    <t>终结本次执行</t>
+  </si>
+  <si>
+    <t>执行完毕</t>
+  </si>
+  <si>
+    <t>退回案件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>移交法院排队立案</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资料不足</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>写诉讼状中</t>
-  </si>
-  <si>
-    <t>资料不足</t>
-  </si>
-  <si>
-    <t>移交法院排队立案</t>
-  </si>
-  <si>
-    <t>诉讼立案</t>
-  </si>
-  <si>
-    <t>已开庭</t>
-  </si>
-  <si>
-    <t>已裁判</t>
-  </si>
-  <si>
-    <t>债务履行完毕结案</t>
-  </si>
-  <si>
-    <t>银行要求撤诉</t>
-  </si>
-  <si>
-    <t>终结执行</t>
-  </si>
-  <si>
-    <t>跟进调解履行情况</t>
-  </si>
-  <si>
-    <t>写执行申请资料</t>
-  </si>
-  <si>
-    <t>移交法院执行手续</t>
-  </si>
-  <si>
-    <t>执行排队立案中</t>
-  </si>
-  <si>
-    <t>执行和解</t>
-  </si>
-  <si>
-    <t>网络查控资产情况</t>
-  </si>
-  <si>
-    <t>扣划工资工积金处置抵押物</t>
-  </si>
-  <si>
-    <t>询价查看不动产情况</t>
-  </si>
-  <si>
-    <t>拍卖抵押物</t>
-  </si>
-  <si>
-    <t>终本</t>
-  </si>
-  <si>
-    <t>恢复执行中</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>银行要求暂不起诉</t>
-  </si>
-  <si>
-    <t>银行未交诉讼费撤诉</t>
-  </si>
-  <si>
-    <t>被告已还清不起诉</t>
-  </si>
-  <si>
-    <t>被告已还清撤诉</t>
-  </si>
-  <si>
-    <t>执行盖章中</t>
-  </si>
-  <si>
-    <t>诉讼盖章中</t>
-  </si>
-  <si>
-    <t>资料未齐全</t>
-  </si>
-  <si>
-    <t>资料齐全律所正在准备诉状或正在盖章</t>
-  </si>
-  <si>
-    <t>资料齐全已移交法院排队</t>
-  </si>
-  <si>
-    <t>立案后调解</t>
-  </si>
-  <si>
-    <t>立案前调解</t>
-  </si>
-  <si>
-    <t>已立案我行申请撤诉</t>
-  </si>
-  <si>
-    <t>未立案我行申请不诉</t>
-  </si>
-  <si>
-    <t>已立案未判决</t>
-  </si>
-  <si>
-    <t>已立案判决未申请执行</t>
-  </si>
-  <si>
-    <t>已申请执行</t>
-  </si>
-  <si>
-    <t>执行中</t>
-  </si>
-  <si>
-    <t>终结本次执行</t>
-  </si>
-  <si>
-    <t>执行完毕</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>银行要求不起诉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1901,7 +1913,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AF1048576" xr:uid="{42D0D285-222E-4112-8984-9734F9F28D29}">
       <formula1>"一般代理,特别代理"</formula1>
     </dataValidation>
@@ -1923,6 +1935,9 @@
       <formula1>-9999999999</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="BT1:BT1048576" xr:uid="{2A93A340-6A3A-4C59-9251-D4460E9536DB}">
+      <formula1>"个贷,房贷,信用卡,普惠"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
@@ -1940,7 +1955,7 @@
           </x14:formula1>
           <xm:sqref>Y1:Y1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" errorStyle="information" allowBlank="1" showInputMessage="1" promptTitle="提示" prompt="如为银行案件请点击单元格右侧下拉菜单选择对应银行" xr:uid="{D4A0A9C7-A2CD-4941-82DA-EF0FEB00F59C}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="提示" prompt="如为银行案件请点击单元格右侧下拉菜单选择对应银行" xr:uid="{D4A0A9C7-A2CD-4941-82DA-EF0FEB00F59C}">
           <x14:formula1>
             <xm:f>下拉菜单!$C$1:$C$8</xm:f>
           </x14:formula1>
@@ -1952,17 +1967,17 @@
           </x14:formula1>
           <xm:sqref>BN1:BN1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{30DA0B9C-AA69-412C-966A-84DD4AAAAF56}">
-          <x14:formula1>
-            <xm:f>下拉菜单!$E$1:$E$26</xm:f>
-          </x14:formula1>
-          <xm:sqref>BO1:BO1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{44A50DD6-510D-4E7B-A823-C35FED0FE2D4}">
           <x14:formula1>
             <xm:f>下拉菜单!$F$1:$F$15</xm:f>
           </x14:formula1>
           <xm:sqref>BP1:BP1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{30DA0B9C-AA69-412C-966A-84DD4AAAAF56}">
+          <x14:formula1>
+            <xm:f>下拉菜单!$E$1:$E$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>BO1:BO1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2064,11 +2079,11 @@
       <c r="D1" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>194</v>
+      <c r="E1" s="11" t="s">
+        <v>232</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2084,11 +2099,11 @@
       <c r="D2" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>195</v>
+      <c r="E2" s="11" t="s">
+        <v>231</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2104,11 +2119,11 @@
       <c r="D3" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>196</v>
+      <c r="E3" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2124,11 +2139,11 @@
       <c r="D4" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>197</v>
+      <c r="E4" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2145,10 +2160,10 @@
         <v>169</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2165,10 +2180,10 @@
         <v>170</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2182,10 +2197,10 @@
         <v>192</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2199,10 +2214,10 @@
         <v>171</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2213,10 +2228,10 @@
         <v>172</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2227,10 +2242,10 @@
         <v>173</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2241,10 +2256,10 @@
         <v>174</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>204</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2255,10 +2270,10 @@
         <v>175</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2267,10 +2282,10 @@
         <v>176</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2278,10 +2293,10 @@
         <v>177</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2289,10 +2304,10 @@
         <v>178</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2300,7 +2315,7 @@
         <v>179</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="4:5">
@@ -2308,7 +2323,7 @@
         <v>180</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="4:5">
@@ -2316,7 +2331,7 @@
         <v>181</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="4:5">
@@ -2324,7 +2339,7 @@
         <v>182</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="4:5">
@@ -2332,7 +2347,7 @@
         <v>183</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="4:5">
@@ -2340,23 +2355,23 @@
         <v>184</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="4:5">
       <c r="D22" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>215</v>
+      <c r="E22" s="11" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="4:5">
       <c r="D23" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>216</v>
+      <c r="E23" s="11" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="24" spans="4:5">
@@ -2364,7 +2379,7 @@
         <v>187</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="4:5">
@@ -2372,7 +2387,7 @@
         <v>188</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="4:5">
@@ -2380,17 +2395,23 @@
         <v>189</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="4:5">
       <c r="D27" s="11" t="s">
         <v>193</v>
       </c>
+      <c r="E27" s="10" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="28" spans="4:5">
       <c r="D28" s="10" t="s">
         <v>190</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="4:5">

--- a/back_end/FastAPI/static/template/case_import_template.xlsx
+++ b/back_end/FastAPI/static/template/case_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\syls\back_end\FastAPI\static\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED45482-E67F-4396-9CDA-BBCE7D0FD948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975015A2-7892-4421-9F98-04B7E3964FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="236">
   <si>
     <t>委托日期</t>
   </si>
@@ -902,6 +902,10 @@
   </si>
   <si>
     <t>银行要求不起诉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>贷款种类</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1365,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DU3"/>
+  <dimension ref="A1:DV3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -1392,13 +1396,13 @@
     <col min="65" max="65" width="26.77734375" customWidth="1"/>
     <col min="66" max="67" width="18" customWidth="1"/>
     <col min="68" max="68" width="21.21875" customWidth="1"/>
-    <col min="69" max="116" width="18" customWidth="1"/>
-    <col min="117" max="117" width="25.109375" customWidth="1"/>
-    <col min="118" max="124" width="18" customWidth="1"/>
-    <col min="125" max="125" width="23" customWidth="1"/>
+    <col min="69" max="117" width="18" customWidth="1"/>
+    <col min="118" max="118" width="25.109375" customWidth="1"/>
+    <col min="119" max="125" width="18" customWidth="1"/>
+    <col min="126" max="126" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:125">
+    <row r="1" spans="1:126">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -1614,166 +1618,169 @@
         <v>39</v>
       </c>
       <c r="BU1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="BV1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CU1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CV1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CW1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CX1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="DA1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DB1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DC1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DD1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DE1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DF1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DG1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DH1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DI1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DJ1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DK1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="DK1" s="1" t="s">
+      <c r="DL1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="DL1" s="1" t="s">
+      <c r="DM1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="DM1" s="1" t="s">
+      <c r="DN1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="DN1" s="1" t="s">
+      <c r="DO1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="DO1" s="1" t="s">
+      <c r="DP1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="DP1" s="1" t="s">
+      <c r="DQ1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="DQ1" s="1" t="s">
+      <c r="DR1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="DR1" s="1" t="s">
+      <c r="DS1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="DS1" s="1" t="s">
+      <c r="DT1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="DT1" s="1" t="s">
+      <c r="DU1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="DU1" s="1" t="s">
+      <c r="DV1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:125">
+    <row r="2" spans="1:126">
       <c r="A2" s="2" t="s">
         <v>93</v>
       </c>
@@ -1907,42 +1914,44 @@
       <c r="DS2" s="2"/>
       <c r="DT2" s="2"/>
       <c r="DU2" s="2"/>
-    </row>
-    <row r="3" spans="1:125">
+      <c r="DV2" s="2"/>
+    </row>
+    <row r="3" spans="1:126">
       <c r="B3" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="7">
+  <dataValidations xWindow="522" yWindow="377" count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AF1:AF1048576" xr:uid="{42D0D285-222E-4112-8984-9734F9F28D29}">
       <formula1>"一般代理,特别代理"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="AU1:AY1048576 CO1:CO1048576 CP1:CP1048576 CU1:CU1048576" xr:uid="{4464FD37-F9F7-4812-BDD0-74E3B51C122E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="AU1:AY1048576 CP1:CP1048576 CQ1:CQ1048576 CV1:CV1048576" xr:uid="{4464FD37-F9F7-4812-BDD0-74E3B51C122E}">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="CK1:CK1048576" xr:uid="{DF26E270-6DC0-4AFD-AA4B-27A7D308895F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="CL1:CL1048576" xr:uid="{DF26E270-6DC0-4AFD-AA4B-27A7D308895F}">
       <formula1>"判决,裁定,调解"</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须使用-或/进行分隔" sqref="B1:B1048576" xr:uid="{76EC1C81-A985-4B80-8417-4F39E45BF715}">
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须为-或/" sqref="AC1:AC1048576 AK1:AK1048576 AL1:AL1048576 AM1:AM1048576 AZ1:AZ1048576 BA1:BA1048576 BE1:BE1048576 BG1:BG1048576 BI1:BI1048576 BJ1:BJ1048576 BK1:BK1048576 BL1:BL1048576 BY1:BY1048576 BZ1:BZ1048576 CB1:CB1048576 CA1:CA1048576 CC1:CC1048576 CG1:CG1048576 CH1:CH1048576 CJ1:CJ1048576 CR1:CR1048576 CV1:CV1048576 CW1:CW1048576 DD1:DD1048576 DE1:DE1048576 DF1:DF1048576 DG1:DG1048576 DH1:DH1048576 DL1:DL1048576 DN1:DN1048576 DP1:DP1048576 DQ1:DQ1048576 DR1:DR1048576" xr:uid="{CA5C5D4D-7B3F-4AD6-8F9A-9FFBDB572669}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="日期分隔符必须为-或/" sqref="AC1:AC1048576 AK1:AK1048576 AL1:AL1048576 AM1:AM1048576 AZ1:AZ1048576 BA1:BA1048576 BE1:BE1048576 BG1:BG1048576 BI1:BI1048576 BJ1:BJ1048576 BK1:BK1048576 BL1:BL1048576 BZ1:BZ1048576 CA1:CA1048576 CC1:CC1048576 CB1:CB1048576 CD1:CD1048576 CH1:CH1048576 CI1:CI1048576 CK1:CK1048576 CS1:CS1048576 CW1:CW1048576 CX1:CX1048576 DE1:DE1048576 DF1:DF1048576 DG1:DG1048576 DH1:DH1048576 DI1:DI1048576 DM1:DM1048576 DO1:DO1048576 DQ1:DQ1048576 DR1:DR1048576 DS1:DS1048576" xr:uid="{CA5C5D4D-7B3F-4AD6-8F9A-9FFBDB572669}">
       <formula1>1</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="当前输入格式非纯数字格式" sqref="AB1:AB1048576 BF1:BF1048576 BH1:BH1048576 BV1:BV1048576 BW1:BW1048576 BX1:BX1048576 CM1:CM1048576 CN1:CN1048576 CX1:CX1048576 CY1:CY1048576 DJ1:DJ1048576 DS1:DS1048576" xr:uid="{2CD1D548-3868-45C8-A9C8-D03CD7D9AEAE}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="提示" error="当前输入格式非纯数字格式" sqref="AB1:AB1048576 BF1:BF1048576 BH1:BH1048576 BW1:BW1048576 BX1:BX1048576 BY1:BY1048576 CN1:CN1048576 CO1:CO1048576 CY1:CY1048576 CZ1:CZ1048576 DK1:DK1048576 DT1:DT1048576" xr:uid="{2CD1D548-3868-45C8-A9C8-D03CD7D9AEAE}">
       <formula1>-9999999999</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="BT1:BT1048576" xr:uid="{2A93A340-6A3A-4C59-9251-D4460E9536DB}">
       <formula1>"个贷,房贷,信用卡,普惠"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" sqref="BU1:BU1048576" xr:uid="{9183054B-50BF-4B63-A679-9F570E167A4C}"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xWindow="522" yWindow="377" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="注意" prompt="请点击单元格右侧下拉菜单进行选择" xr:uid="{FC007753-7F4D-4AE2-8418-3AD9DF4FEF31}">
           <x14:formula1>
             <xm:f>下拉菜单!$A$1:$A$12</xm:f>
